--- a/ch-2-working-with-visuals-and-dataframes/ch_02_solutions.xlsx
+++ b/ch-2-working-with-visuals-and-dataframes/ch_02_solutions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\AI-Powered-Analytics-in-Excel\ch-2-working-with-visuals-and-dataframes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F20A4C-9494-4E20-9C29-613651B78CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8135716E-2DB6-4258-ADDE-1D5614BFD08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,10 +699,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1865,7 +1865,7 @@
   <autoFilter ref="A1:C6" xr:uid="{456FF165-CB56-407D-8222-C9F0935D7D60}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{26945669-7A59-44A7-9525-9771AA042A42}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{FE6E5257-1713-4391-A556-ABA4C561800A}" name="population" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{FE6E5257-1713-4391-A556-ABA4C561800A}" name="population" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{AF7C1BFD-6695-479C-BA7C-EDD9506AC8E9}" name="land_area"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1883,7 +1883,7 @@
     <tableColumn id="5" xr3:uid="{0CF12FFC-440B-4558-A81F-0AF8CD0C48F6}" name="category"/>
     <tableColumn id="6" xr3:uid="{CFE94FFA-7BCC-4343-BCA8-E2B024064CED}" name="unit_price"/>
     <tableColumn id="7" xr3:uid="{21D4AEB3-F0C3-4A67-8243-2C0ACC40D02E}" name="quantity"/>
-    <tableColumn id="8" xr3:uid="{DEB97BAB-FFF9-4832-B094-E6D1DF5758DB}" name="order_date" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{DEB97BAB-FFF9-4832-B094-E6D1DF5758DB}" name="order_date" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{B2FC4691-F5E9-44A5-930A-1449BCEB64C5}" name="customer_age"/>
     <tableColumn id="10" xr3:uid="{9392215B-51B6-4853-8E99-0AEA99EF02BC}" name="customer_gender"/>
     <tableColumn id="11" xr3:uid="{494D33B1-0FD9-43EA-A6B7-627E2DD6A55E}" name="country"/>
